--- a/healthcare_forms/009_weight_loss_intake_form--healthcare_forms.xlsx
+++ b/healthcare_forms/009_weight_loss_intake_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,8 +773,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -802,12 +802,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'high_blood_pressure'}</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'High Blood Pressure'}</t>
+          <t>High Blood Pressure</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'heart_disease'}</t>
+          <t>heart_disease</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Heart Disease'}</t>
+          <t>Heart Disease</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'obesity'}</t>
+          <t>obesity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Obesity'}</t>
+          <t>Obesity</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'all_of_the_above'}</t>
+          <t>all_of_the_above</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'All of the above'}</t>
+          <t>All of the above</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'nutrition_counseling'}</t>
+          <t>nutrition_counseling</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Nutrition Counseling'}</t>
+          <t>Nutrition Counseling</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'medication'}</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Medication'}</t>
+          <t>Medication</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'exercise'}</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Exercise'}</t>
+          <t>Exercise</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'surgery'}</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Surgery'}</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'general_health'}</t>
+          <t>general_health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'General Health'}</t>
+          <t>General Health</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'weight_loss'}</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Weight Loss'}</t>
+          <t>Weight Loss</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'cardiology'}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Cardiology'}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'gastroenterology'}</t>
+          <t>gastroenterology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Gastroenterology'}</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'nephrology'}</t>
+          <t>nephrology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Nephrology'}</t>
+          <t>Nephrology</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'pulmonology'}</t>
+          <t>pulmonology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Pulmonology'}</t>
+          <t>Pulmonology</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'endocrinology'}</t>
+          <t>endocrinology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Endocrinology'}</t>
+          <t>Endocrinology</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'gynecology'}</t>
+          <t>gynecology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Gynecology'}</t>
+          <t>Gynecology</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'urology'}</t>
+          <t>urology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Urology'}</t>
+          <t>Urology</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
